--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,22 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/floswald/.julia/dev/JPEtools/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diegogonzalezgonzalez/Desktop/Data Replicator/JPE/JPE-Soltas-20241011/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957E4354-791A-4942-ABF7-9C88724FEAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80955A17-F4B9-464C-A03B-E20461122A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="21900" windowHeight="12060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="228">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -46,6 +58,669 @@
   </si>
   <si>
     <t>In-text numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Figure/Table #    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Program                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Line Number </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Output file                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Note                            </t>
+  </si>
+  <si>
+    <t>-------------------</t>
+  </si>
+  <si>
+    <t>--------------------------------</t>
+  </si>
+  <si>
+    <t>-------------</t>
+  </si>
+  <si>
+    <t>--------------------------------------------------------------------</t>
+  </si>
+  <si>
+    <t>---------------------------------</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Table 1           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02_analysis/table1.do          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> summarystats.csv                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Table 2           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 02_analysis/table2and3.do      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> table2.csv                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Table 3           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> table3.csv                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Figure 1, Panel A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_1ab_A23ab_A28ab.do </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg.csv; figures/eligregs_appear_2_c_no3.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Program generates other figures not included in the paper </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Figure 1, Panel B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg.csv; figures/eligregs_appear_2_eq_no.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Figure 1, Panel C </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_1c.do              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_within.csv; figures/eligregs_between_within_lifetime.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Figure 1, Panel D </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_1d.do              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_mu.csv; figures/participation_reg_mu.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Figure 2 	    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_2_A23d.do          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_cex.csv; figures/eligregs_psid_cex.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_A1.do          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_ui_wc_ss.csv; figures/participation_reg_ui_wc_ss.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 2, Panel A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_A2ab.do          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_robustness11.csv; figures/eligregs_robustness_11_c.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 2, Panel B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_robustness11.csv; figures/eligregs_robustness_11_li.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_A3.do          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/friedman_binscatter.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_A4.do          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fgiures/friedman_binscatter.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_A5.do          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_robustness8.csv; figures/eligregs_robustness_8_c.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 6, Panel A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_A6ab.do          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_robustness11.csv; figures/eligregs_appear_2_c_no3hh.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 6, Panel B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_hh.csv; figures/eligregs_appear_2_hh_nohh.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 7, Panel A </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_A7ab.do          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_robustness4.csv; figures/eligregs_robustness_4_c.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 7, Panel B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_robustness4.csv; figures/eligregs_robustness_4_li.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Appendix Figure 8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> analyze/fig_A8.do          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> figures/participation_reg_robustness_rpp.csv; figures/participation_reg_robustness_rpp.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Figure created will appear different than corresponding figure in the paper due to the removal of proprietary data </t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Table A1</t>
+  </si>
+  <si>
+    <t>Table A2</t>
+  </si>
+  <si>
+    <t>Table A3</t>
+  </si>
+  <si>
+    <t>Table A4</t>
+  </si>
+  <si>
+    <t>Table A5</t>
+  </si>
+  <si>
+    <t>Table A6</t>
+  </si>
+  <si>
+    <t>Table A7</t>
+  </si>
+  <si>
+    <t>Table A8</t>
+  </si>
+  <si>
+    <t>Table A9</t>
+  </si>
+  <si>
+    <t>Table A10</t>
+  </si>
+  <si>
+    <t>Table A11</t>
+  </si>
+  <si>
+    <t>Table A12</t>
+  </si>
+  <si>
+    <t>Table A13</t>
+  </si>
+  <si>
+    <t>Table A14</t>
+  </si>
+  <si>
+    <t>Table A17</t>
+  </si>
+  <si>
+    <t>analyze/table_2_A1.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A2.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A3.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A4_i; table_A4_ii.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A5.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A6.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A7_A8.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A9.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A10_12.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A11_13.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A14.do</t>
+  </si>
+  <si>
+    <t>24–35</t>
+  </si>
+  <si>
+    <t>analyze/table_1.do</t>
+  </si>
+  <si>
+    <t>analyze/table_A17.do; analyze/table_3_iii.do</t>
+  </si>
+  <si>
+    <t>analyze/welfare_progs.do; analyze/table_3_ii.do; analyze/table_3_iii.do</t>
+  </si>
+  <si>
+    <t>emp_mvpf_crramain_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_mvpf_crramain_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_mvpf_crramain_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_mvpf_crramain_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_mvpf_crramain_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_mvpf_crramain_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_mvpf_crramain_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_mvpf_crramain_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraavgmuelig_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraavgmuelig_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraavgmuelig_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraavgmuelig_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraavgmuelig_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraavgmuelig_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraavgmuelig_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraavgmuelig_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraelig_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraelig_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraelig_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraelig_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraelig_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraelig_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraelig_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraelig_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetihalf_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetihalf_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetihalf_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetihalf_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetihalf_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetihalf_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetihalf_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetihalf_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetitwice_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetitwice_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetitwice_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetitwice_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetitwice_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetitwice_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetitwice_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crraetitwice_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrali_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrali_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrali_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrali_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrali_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrali_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrali_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrali_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crralp_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crralp_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crralp_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crralp_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crralp_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crralp_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crralp_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crralp_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramain_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramain_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramain_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramain_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramain_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramain_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramain_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramain_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramp_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramp_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramp_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramp_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramp_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramp_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramp_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crramp_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrara2_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrara2_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrara2_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrara2_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrara2_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrara2_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrara2_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrara2_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrarahalf_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrarahalf_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrarahalf_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrarahalf_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrarahalf_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrarahalf_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrarahalf_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrarahalf_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratahalf_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratahalf_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratahalf_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratahalf_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratahalf_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratahalf_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratahalf_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratahalf_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratatwice_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratatwice_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratatwice_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratatwice_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratatwice_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratatwice_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratatwice_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crratatwice_wic.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrautil_ha.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrautil_liheap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrautil_medicaid.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrautil_schoolmeals.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrautil_snap.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrautil_ssi.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrautil_tanf.dta</t>
+  </si>
+  <si>
+    <t>emp_welfare_crrautil_wic.dta</t>
+  </si>
+  <si>
+    <t>mvpf_for_table_crramain.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crraavgmuelig.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crraetihalf.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crraetitwice.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crralp.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crramain.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crramp.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crrangs.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crrara2.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crrarahalf.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crratahalf.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crratatwice.dta</t>
+  </si>
+  <si>
+    <t>welfare_for_table_crrautil.dta</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -118,7 +793,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -434,13 +1109,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
@@ -485,23 +1161,2115 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
+      <c r="A2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2">
+        <v>146</v>
+      </c>
+      <c r="H2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
+      <c r="A3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3">
+        <v>129</v>
+      </c>
+      <c r="H3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H4" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5">
+        <v>649</v>
+      </c>
+      <c r="H5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6">
+        <v>591</v>
+      </c>
+      <c r="H6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7">
+        <v>213</v>
+      </c>
+      <c r="H7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8">
+        <v>206</v>
+      </c>
+      <c r="H8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9">
+        <v>210</v>
+      </c>
+      <c r="H9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10">
+        <v>136</v>
+      </c>
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11">
+        <v>256</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12">
+        <v>256</v>
+      </c>
+      <c r="H12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13">
+        <v>98</v>
+      </c>
+      <c r="H13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14">
+        <v>141</v>
+      </c>
+      <c r="H14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15">
+        <v>181</v>
+      </c>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16">
+        <v>299</v>
+      </c>
+      <c r="H16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17">
+        <v>283</v>
+      </c>
+      <c r="H17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18">
+        <v>226</v>
+      </c>
+      <c r="H18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19">
+        <v>226</v>
+      </c>
+      <c r="H19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20">
+        <v>231</v>
+      </c>
+      <c r="H20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21">
+        <v>129</v>
+      </c>
+      <c r="H21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22">
+        <v>109</v>
+      </c>
+      <c r="H22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23">
+        <v>142</v>
+      </c>
+      <c r="H23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24">
+        <v>163</v>
+      </c>
+      <c r="H24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25">
+        <v>108</v>
+      </c>
+      <c r="H25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26">
+        <v>557</v>
+      </c>
+      <c r="H26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27">
+        <v>100</v>
+      </c>
+      <c r="H27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28">
+        <v>100</v>
+      </c>
+      <c r="H28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29">
+        <v>74</v>
+      </c>
+      <c r="H29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" t="s">
+        <v>81</v>
+      </c>
+      <c r="F30" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30">
+        <v>109</v>
+      </c>
+      <c r="H30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" t="s">
+        <v>82</v>
+      </c>
+      <c r="F31" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31">
+        <v>95</v>
+      </c>
+      <c r="H31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" t="s">
+        <v>95</v>
+      </c>
+      <c r="G32">
+        <v>101</v>
+      </c>
+      <c r="H32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" t="s">
+        <v>96</v>
+      </c>
+      <c r="G33">
+        <v>87</v>
+      </c>
+      <c r="H33" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" t="s">
+        <v>97</v>
+      </c>
+      <c r="G34">
+        <v>64</v>
+      </c>
+      <c r="H34" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" t="s">
+        <v>86</v>
+      </c>
+      <c r="F35" t="s">
+        <v>100</v>
+      </c>
+      <c r="G35">
+        <v>38</v>
+      </c>
+      <c r="H35" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>137</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>138</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>139</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>142</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>146</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>147</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>148</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>151</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C53" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>154</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>155</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C55" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>156</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>157</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C57" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>158</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>159</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C59" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>160</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>162</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>163</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C63" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>165</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>166</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>168</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C68" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>169</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C69" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>171</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>172</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>173</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C73" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>174</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C74" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>175</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C75" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C76" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>177</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C77" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>178</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C78" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>179</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>180</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C80" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>181</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C82" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C83" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>184</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C84" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>185</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C85" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>186</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C86" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>187</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C87" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>188</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C88" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>189</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C89" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>190</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C90" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>191</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C91" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>192</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C92" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>193</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C93" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>194</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C94" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>195</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C95" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>196</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C96" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>197</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C97" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>198</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C98" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>199</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C99" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>200</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C100" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>201</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C101" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C102" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>203</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C103" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>204</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C104" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>205</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C105" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>206</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C106" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>207</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C107" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>208</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C108" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>209</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C109" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>210</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C110" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>211</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C111" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>212</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C112" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>213</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C113" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>214</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C114" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>215</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C115" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>216</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C116" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>217</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C117" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>218</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C118" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>219</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C119" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>220</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C120" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>221</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C121" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>222</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C122" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>223</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C123" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>224</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C124" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>225</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C125" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>226</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C126" t="s">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51360285-2046-394F-B3CC-D7A91F452654}">
+  <dimension ref="B1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>649</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>145</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>649</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>591</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8">
+        <v>213</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>206</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10">
+        <v>210</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11">
+        <v>136</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12">
+        <v>256</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13">
+        <v>256</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14">
+        <v>98</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15">
+        <v>141</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16">
+        <v>181</v>
+      </c>
+      <c r="E16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17">
+        <v>299</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18">
+        <v>283</v>
+      </c>
+      <c r="E18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19">
+        <v>226</v>
+      </c>
+      <c r="E19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20">
+        <v>226</v>
+      </c>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21">
+        <v>231</v>
+      </c>
+      <c r="E21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/package-output-map.xlsx
+++ b/package-output-map.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diegogonzalezgonzalez/Desktop/Data Replicator/JPE/JPE-Soltas-20241011/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80955A17-F4B9-464C-A03B-E20461122A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACDBFFA-CB8E-354B-8DC4-621571FCC078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="227">
   <si>
     <t>Data Preparation Program</t>
   </si>
@@ -718,9 +718,6 @@
   </si>
   <si>
     <t>welfare_for_table_crrautil.dta</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1223,7 @@
         <v>98</v>
       </c>
       <c r="H4" t="s">
-        <v>227</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
